--- a/src/assets/excel/Attendee Speaker template.xlsx
+++ b/src/assets/excel/Attendee Speaker template.xlsx
@@ -1,29 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eventita_ui\src\assets\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1276701F-0458-4C09-B903-1D919313C817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="720" yWindow="1584" windowWidth="17280" windowHeight="8988" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="82">
   <si>
     <t>First Name</t>
   </si>
@@ -37,106 +25,461 @@
     <t>Organisation</t>
   </si>
   <si>
-    <t>Role</t>
+    <t>Designation</t>
   </si>
   <si>
     <t>Group</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>William</t>
-  </si>
-  <si>
-    <t>Magwood</t>
-  </si>
-  <si>
-    <t>w.magwood@oecd-nea.org</t>
-  </si>
-  <si>
-    <t>Nuclear Energy Agency (NEA)</t>
-  </si>
-  <si>
-    <t>Director-General</t>
-  </si>
-  <si>
-    <t>Speaker</t>
-  </si>
-  <si>
-    <t>A leading global advocate for nuclear safety and policy, William oversees international cooperation at the NEA, focusing on the intersection of technology, economics, and social policy in the nuclear sector.</t>
+    <t>Bio</t>
+  </si>
+  <si>
+    <t>Dr. Supratim</t>
+  </si>
+  <si>
+    <t>Basu</t>
+  </si>
+  <si>
+    <t>sb@drbose.com</t>
+  </si>
+  <si>
+    <t>Dr. Bose Institute</t>
+  </si>
+  <si>
+    <t>Managing Director and CEO</t>
+  </si>
+  <si>
+    <t>Tutorial Speaker, Speaker</t>
+  </si>
+  <si>
+    <t>Over 30 years of pureplay immersion in Power Electronics Research and Design. Demonstrated expertise in blending innovative application of Technology with astute commercial thought. Successful history of New Product Development, Business and Organizational Management, and Driving Profitability. Acquiring Projects from global customers and leveraging sensitivity to cultural nuances of European &amp; American clients, towards building effective relationships. Extensive experience in Teaching and Academic Research, in University environments.
+ Ph.D.Power Electronics, Chalmers University of Technology, Sweden
+ M.Tech, Power Electronics, Indian Institute of Science, Bangalore B.E.
+ Electrical &amp; Electronics, Birla Institute of Technology, Mesra
+ Power Electronics Design
+ SWITCHMODE POWER SUPPLIES, CHARGERS, INVERTERS &amp; UPS UPTO 30 KW Years of practical hands-on experience in designing, building, debugging &amp; testing of converters including EMI and Safety compliance for Industrial, Medical, Telecommunications, Automotive, and Military business verticals.
+ Project &amp; Project Acquisitions
+ CUSTOMER ENGAGEMENT, REVIEWS, PRE-STUDY &amp; CONTRACTING 25+ Years of experience in acquiring Power Electronics R&amp;D Projects from Customers in USA &amp; Europe. Deliverables being, either, creating Technology Roadmaps, Study Reports &amp; Feasibility Studies. Or, the Development of New Products - requiring design, prototyping, certification, and Transfer of Technology.
+ Created multiple IPs in Power Electronics design
+ Multiple first-author publications in IEEE and EPE journals &amp; conferences
+ Multiple tutorials to global audiences in IEEE and EPE Power Electronics conferences in USA &amp; Europe
+ Delivered multiple lectures and co-supervised international Ph.D. students with IEEE publications
+ Training and Consulting with many Global corporations</t>
+  </si>
+  <si>
+    <t>Prof. Mohan Lal</t>
+  </si>
+  <si>
+    <t>Kolhe</t>
+  </si>
+  <si>
+    <t>ml.kolhe@testmail.com</t>
+  </si>
+  <si>
+    <t>University of Agder, Norway</t>
+  </si>
+  <si>
+    <t>Professor</t>
+  </si>
+  <si>
+    <t>Dr. Ritula</t>
+  </si>
+  <si>
+    <t>Thakur</t>
+  </si>
+  <si>
+    <t>r.thakur@testmail.com</t>
+  </si>
+  <si>
+    <t>Electrical Engineering Department
+ National Institute of Technical Teachers Training and Research, Chandigarh, India</t>
+  </si>
+  <si>
+    <t>Associate Professor &amp; Head</t>
+  </si>
+  <si>
+    <t>Prof. Avoki Michel</t>
+  </si>
+  <si>
+    <t>Omekanda</t>
+  </si>
+  <si>
+    <t>am.omekanda@testmail.com</t>
+  </si>
+  <si>
+    <t>Propulsion Systems Research Lab
+ General Motors Global R&amp;D Center, Warren, MI, USA</t>
+  </si>
+  <si>
+    <t>Staff Research Engineer</t>
+  </si>
+  <si>
+    <t>Keynote Speaker, Speaker</t>
+  </si>
+  <si>
+    <t>Dr. Omekanda received the M.Sc. degree in electrical and mechanical engineering from the Free University of Brussels (Universite Libre de Bruxelles), Belgium in 1992 and 1995, respectively. In 1997, He received the Ph.D. degree in Electromechanical Engineering from the University of Liège, Belgium. He has about thirty years of experience in the design of electrical machines (Switched Reluctance Motors, Permanent Magnet Synchronous Motors, and Induction Motors) spanning academia and industry. From 1992 to 1999, he held Research Associate positions at the Free University of Brussels and the University of Liège, Belgium, before joining Delphi Automotive Systems, Saginaw, MI, USA, from 1999 to 2001 as a Senior Research Engineer. Since 2001, he has been with the General Motors Research &amp; Development Center, Warren, MI, where he is currently a Staff Research Engineer at the Propulsion Systems Research Lab. Dr. Omekanda has authored and coauthored more than 60 technical papers and holds twelve issued U.S. patents. He is President-Elect of the IEEE Industry Applications Society (IAS). He served as President of the IEEE IAS Industrial Drives Committee (2021-2022) and Vice-President of the IEEE IAS Renewable &amp; Sustainable Energy Conversion Systems Department (2022-2024). He is an IAS Distinguished Lecturer since 2015. Dr. Omekanda is a Fellow of the IEEE.</t>
+  </si>
+  <si>
+    <t>Prof. Babu</t>
+  </si>
+  <si>
+    <t>Chalamala</t>
+  </si>
+  <si>
+    <t>b.chalamala@testmail.com</t>
+  </si>
+  <si>
+    <t>Department of Electrical and Computer Engineering
+ The University of Texas at Dallas, Richardson, TX, USA</t>
+  </si>
+  <si>
+    <t>Dr. Babu Chalamala is a professor of Electrical and Computer Engineering Department at the University of Texas at Dallas, Richardson, TX, USA. Prior to joining UTD, he was the manager of the Grid Energy Storage Department and the Energy Storage Technology and Systems Group at Sandia National Laboratories, Albuquerque, NM, USA. He has over three decades of R&amp;D experience across industry, national lab, and academia. He is recognized for his research in energy storage, electronic materials and devices, and nanotechnology, that has led to more than 200 publications and 14 issued US patents. His current research interests are in battery, flow battery, supercapacitor, and hybrid technology. He is actively involved in grid-scale stationary storage and EV integration where he led major engagements with utilities and the automotive industry. Dr. Chalamala received his PhD in Physics from the University of North Texas. He is a Fellow of IEEE, the Society for Information Display (SID), and American Physical Society (APS). His IEEE volunteer activities include serving as Vice President of Conferences of the IEEE Power and Energy Society and the Chair of the IEEE-USA Energy Policy Committee. Earlier, he served as the chair of the Long-Range Planning Committee, and a member of the Governance Committee of IEEE-PES. He also served as the chair of the IEEE Nanotechnology Council.</t>
+  </si>
+  <si>
+    <t>Prof. Marta</t>
+  </si>
+  <si>
+    <t>Molinas</t>
+  </si>
+  <si>
+    <t>m.molinas@testmail.com</t>
+  </si>
+  <si>
+    <t>Department of Engineering Cybernetics
+ Norwegian University of Science and Technology (NTNU), Norway</t>
+  </si>
+  <si>
+    <t>Marta Molinas (Fellow, IEEE) received the Diploma degree in electromechanical engineering from the National University of Asuncion, Asuncion, Paraguay, in 1992, the M.Sc. degree from the University of the Ryukyus, Nishihara, Japan, in 1997, and the D.Eng. degree from the Tokyo Institute of Technology, Tokyo, Japan, in 2000. She was a Guest Researcher with the University of Padova, Padova, Italy, in 1998. From 2004 to 2007, she was a Postdoctoral Researcher with the Norwegian University of Science and Technology (NTNU), Trondheim, Norway, where she has been a Professor in 2008 within the Department of Engineering Cybernetics. From 2008 to 2009, she was a JSPS Research Fellow with the Energy Technology Research Institute, National Institute of Advanced Industrial Science and Technology, Tsukuba, Japan. Her current research interests include stability of power electronics systems, harmonics and oscillations in power electronics dominated power systems, and science of complex systems. Dr. Molinas is currently an Editor-at-Large of the IEEE Industrial Electronics Magazine and was the Editor-in-Chief of the IEEE TRANSACTIONS ON ENERGY CONVERSION. She has been an AdCom Member-at-Large of the IEEE Power Electronics Society from 2019 to 2022.</t>
+  </si>
+  <si>
+    <t>Prof. Mahesh</t>
+  </si>
+  <si>
+    <t>Krishnamurthy</t>
+  </si>
+  <si>
+    <t>m.krishnamurthy@testmail.com</t>
+  </si>
+  <si>
+    <t>Department of Electrical Engineering
+ Southern Methodist University (SMU), Dallas, TX, USA</t>
+  </si>
+  <si>
+    <t>Caruth Institute Chair Professor</t>
+  </si>
+  <si>
+    <t>Dr. Mahesh Krishnamurthy is the Caruth Institute Chair Professor in the Department of Electrical Engineering at Southern Methodist University (SMU), Dallas. He is also the founding director of the Advanced Sustainable Power and Energy Networks (ASPEN) Lab at SMU. His research interests include the design and control of electric machines and power electronic converters. He actively works with industry to develop innovative solutions to real world problems. His research is primarily focused on the electrification of transportation, sustainable energy systems, and grid-based energy infrastructure. He has authored over 175 publications, five book chapters, and has won over 40 prizes and awards. He has also licensed three patents, one of which was for an electric machine that won the 2013 R&amp;D 100 Award. He has been awarded several best paper awards and three of the faculty awards at IIT. He has been a PI on several projects from government agencies and industry which total over $15 million in research funding. Dr. Krishnamurthy served as the chair of the IEEE Transportation Electrification Community (TEC) for 2020-21. He is currently serving as the vice chair of the IEEE TEC steering committee.</t>
+  </si>
+  <si>
+    <t>Mr. Vivek</t>
+  </si>
+  <si>
+    <t>Pandey</t>
+  </si>
+  <si>
+    <t>v.pandey@testmail.com</t>
+  </si>
+  <si>
+    <t>Grid-India, Ministry of Power, Government of India</t>
+  </si>
+  <si>
+    <t>Chief General Manager</t>
+  </si>
+  <si>
+    <t>Mr. Vivek Pandey is the Chief General Manager of Grid-India, where he leads critical grid integration and system operation functions. He is responsible for managing complex technical challenges related to integrating renewable energy resources into the Indian power grid. He has over two decades of experience in the power sector and has played a pivotal role in advancing grid reliability and sustainable energy transitions in India. Under his leadership, Grid-India has been at the forefront of implementing innovative grid management solutions to support India's ambitious renewable energy targets. Mr. Pandey is recognized for his expertise in power system operations, transmission planning, and grid stability analysis. He is a strong advocate for smart grid technologies and grid modernization initiatives that support energy security and sustainability. He has been instrumental in various national-level projects and has collaborated with international organizations for grid management best practices. His contributions have been vital in strengthening the resilience and flexibility of India's electricity infrastructure.</t>
+  </si>
+  <si>
+    <t>Prof. Claudio</t>
+  </si>
+  <si>
+    <t>Canizares</t>
+  </si>
+  <si>
+    <t>c.canizares@testmail.com</t>
+  </si>
+  <si>
+    <t>University of Waterloo, Canada</t>
+  </si>
+  <si>
+    <t>University Professor &amp; Hydro One Endowed Chair</t>
+  </si>
+  <si>
+    <t>Dr. Claudio Cañizares is a University Professor and the Hydro One Endowed Chair at the Electrical and Computer Engineering (E&amp;CE) Department, and the Executive Director of the Waterloo Institute for Sustainable Energy (WISE) at the University of Waterloo, where he has held various academic and administrative positions since 1993 and has received multiple recognitions, in particular the 2021-2022 Awards of Excellence in Graduate Supervision from both the University and the Faculty of Engineering. He obtained the Electrical Engineer degree from the Escuela Politécnica Nacional (EPN) in Quito, Ecuador, in 1984, where he held various academic and administrative positions between 1983 and 1993. His MSc (1988) and PhD (1991) degrees in Electrical Engineering are from the University of Wisconsin-Madison. His research activities focus on the study of stability, control, optimization, modeling, simulation, and computational issues in bulk power systems, microgrids, and energy systems in the context of net-zero, competitive energy markets, smart grids, and energy access. In these areas, he has led or been an integral part of multiple grants and contracts from government agencies and private companies worth over $92 million CAD, and has collaborated with various industry and university partners in Canada and abroad, supervising/co-supervising over 190 research fellows and graduate students. He has authored/co-authored over 400 publications with close to 38,000 citations and an 87 H-index, including journal and conference papers, technical reports, book chapters, disclosures, and patents, and has been invited to deliver keynote speeches, seminars, tutorials, and presentations at many prestigious venues worldwide. Dr. Cañizares was the 2020-2024 Editor-In-Chief of the IEEE Transactions on Smart Grid, the 2022-2023 IEEE Division VII Director of the IEEE and Power &amp; Energy Society (PES) Boards, and is the 2025 Vice-Chair and 2026 Chair of the IEEE Technologies for a Sustainable Climate Matrix Organization (TSCMO). He is a Fellow of the IEEE, a Fellow of the Canadian Academy of Engineering, a Fellow of the Royal Society of Canada, where he was the Director of the Applied Science and Engineering Division of the Academy of Science from 2017 to 2020, and a Foreign Fellow of the Chinese Society for Electrical Engineering. He is also the recipient of the 2025 IEEE PES Ramakumar Family Renewable Energy Excellence Award, the 2017 IEEE PES Outstanding Power Engineering Educator Award, the 2016 IEEE Canada Electric Power Medal, and of multiple IEEE PES awards and recognitions, holding leadership positions in several IEEE and PES Committees, Working Groups, and Task Forces.</t>
+  </si>
+  <si>
+    <t>Prof. Mohammad</t>
+  </si>
+  <si>
+    <t>Nasir Uddin</t>
+  </si>
+  <si>
+    <t>m.nasiruddin@testmail.com</t>
+  </si>
+  <si>
+    <t>Department of Electrical Engineering
+ Lakehead University, Canada</t>
+  </si>
+  <si>
+    <t>Dr. Mohammad Nasir Uddin (Fellow IEEE) received the B.Sc. and M.Sc. degrees both in electrical &amp; electronic engineering from Bangladesh University of Engineering and Technology (BUET), Dhaka, Bangladesh, and the Ph.D. degree in electrical engineering from Memorial University of Newfoundland, Canada in 1993, 1996, and 2000, respectively. He has been serving as a Professor in the Department of Electrical Engineering, Lakehead University (LU), Thunder Bay, ON, Canada since August 2001. He also served as a visiting Prof. at Univ. of Malaya (2013, 2012, 2011), University of Tenaga Nasional (UNITEN) (2018-2019), Malaysia, Tokyo University of Science (2010), Japan and North South University (2006), Dhaka, Bangladesh. Previously, he was an Assistant Professor in the Department of Electrical and Computer Engineering, University of South Alabama, USA from January 2001 to May 2001, an Assistant Professor from 1996 to 1997 and a lecturer from 1994 to 1996 at BUET. He possesses more than 28 years of teaching experience and has authored/co-authored over 290 papers in international journals (75 in IEEE Transactions (top ranking in the field) and 21 in other refereed journals) and conferences. Currently, he is serving as a member of the IEEE Technical Field Award Selection committee. During 2016-2017 he served as an Executive Board Member of IEEE Industry Applications Society (IAS) and Chair of IEEE-IAS-Manufacturing Systems Development and Applications Department. Earlier, he also served as one of the Technical Program Committee Chairs for IEEE Energy Conversion Congress and Expo (ECCE) 2015 at Montreal, Canada. He was the Technical Program Committee Chair for the IEEE-IAS [Industrial Automation and Control Committee (IACC)] Annual Meetings in 2011 (Orlando) and 2012 (Las Vegas). He served as Transactions Papers Review Chair (Editor for four years, 2009–2010 and 2013–2014) for IEEE Transactions on Industry Applications (IACC). Earlier he served IEEE IAS IACC for 9 years in different capacities (secretary-elected, vice-chair, chair and past-chair). Due to his outstanding contributions IEEE-IAS IACC recognized him with the IEEE IAS Service Award 2015. He received several other awards, including the prestigious IEEE Power and Energy Society Cyril Veinott Electromechanical Energy Conversion Award 2025, EIC (Engineering Institute of Canada) Fellow (2023), and IEEE-IAS Distinguished Lecturer (2026-2027). He was also the recipient of the LU both Distinguished Instructor Award (highest instructor award) in 2023 and Distinguished Researcher Award (highest research award) in 2010 and five Prize Paper Awards from IEEE IAS IACC. He is a registered professional engineer in the province of Ontario, Canada. His research interests include renewable energy, motor drives, power system and intelligent controller applications.</t>
+  </si>
+  <si>
+    <t>Prof. Jean</t>
+  </si>
+  <si>
+    <t>Bélanger</t>
+  </si>
+  <si>
+    <t>j.belanger@testmail.com</t>
+  </si>
+  <si>
+    <t>OPAL-RT Technologies</t>
+  </si>
+  <si>
+    <t>Co-Founder, CEO &amp; CTO</t>
+  </si>
+  <si>
+    <t>Prof. Jean Bélanger is the Co-Founder, Chief Executive Officer, and Chief Technology Officer of OPAL-RT TECHNOLOGIES, a global leader in real-time digital simulation and hardware-in-the-loop (HIL) testing solutions. He co-founded OPAL-RT in 1997 with the vision of democratizing high-end real-time simulation tools for engineers and researchers worldwide. Under his strategic and technological leadership, the company has become a renowned developer of state-of-the-art real-time simulators for complex electrical, electro-mechanical, and power electronic systems across industries including automotive, aerospace, energy, and power systems. Jean began his career at Hydro-Québec, where he worked extensively in power system design and simulation and contributed to major projects such as the 765-kV James Bay transmission system. He holds a Bachelor's degree in Electrical Engineering from Laval University and a Master's degree in Power Systems from École Polytechnique de Montréal. Jean is also a Fellow of the Canadian Academy of Engineering, recognizing his significant contributions to engineering and innovation.</t>
+  </si>
+  <si>
+    <t>Prof. Ganesh Kumar</t>
+  </si>
+  <si>
+    <t>Venayagamoorthy</t>
+  </si>
+  <si>
+    <t>g.venayagamoorthy@testmail.com</t>
+  </si>
+  <si>
+    <t>International Neural Network Society;
+ Clemson University, USA</t>
+  </si>
+  <si>
+    <t>President-Elect, Duke Energy Distinguished Professor of Power Engineering</t>
+  </si>
+  <si>
+    <t>Ganesh Kumar Venayagamoorthy is the Duke Energy Distinguished Professor of Power Engineering and Professor of Electrical and Computer Engineering at Clemson University since January 2012. Prior to that, he was a Professor of Electrical and Computer Engineering at the Missouri University of Science and Technology (Missouri S&amp;T), Rolla, USA where he was from 2002 to 2011. Dr. Venayagamoorthy is the Founder and Director of the Real-Time Power and Intelligent Systems Laboratory at Clemson University. Dr. Venayagamoorthy holds the position of an Extraordinary Professor in the Department of Electrical, Electronic and Computer Engineering at the University of Pretoria, South Africa.
+ Dr. Venayagamoorthy received his PhD and MScEng degrees in Electrical Engineering from the University of Natal, Durban, South Africa. He received his BEng degree with a First-Class Honors in Electrical and Electronics Engineering from Abubakar Tafawa Balewa University, Bauchi, Nigeria. He holds an MBA degree in Entrepreneurship and Innovation from Clemson University, USA.
+ Dr. Venayagamoorthy is a recipient of 2004 U.S. NSF CAREER award and 2007 U.S. Office of the Naval Research Young Investigator Award. His research interests are in the development and innovation of power systems, smart grids and artificial intelligence technologies. He is an inventor of technologies for scalable computational intelligence for complex systems and dynamic stochastic optimal power flow. Dr. Venayagamoorthy has published over 600 refereed technical articles which are cited over 26,000 times with a h-index of 75 and i10-index of &gt; 300. Professor Venayagamoorthy has given over 500 technical presentations (including 40 keynotes and plenaries) in 50+ countries to date.
+ Dr. Venayagamoorthy is a Fellow of the IEEE, IET (UK), the South African Institute of Electrical Engineers (SAIEE) and Asia-Pacific Artificial Intelligence Association (AAIA), and a Senior Member of the International Neural Network Society (INNS). He is the 2026 INNS President-Elect. Dr. Venayagamoorthy is the Chair and Founder of the IEEE PES Working Group on Intelligent Control Systems and IEEE Computational Intelligence Society (CIS) Task Force on Smart Grid. He has served/serves as Editor/Associate Editor/Guest Editor of several IEEE Transactions and Elsevier Journals. He is the Editor for the IEEE Press Series on Power and Energy Systems. He is a Distinguished Lecturer of the IEEE CIS, IAS, IES and PES. He was a 2024 U.S. Fulbright Scholar to South Africa. He is the General Chair for 2027 INNS-IEEE International Joint Conference on Neural Networks, Cape Town, South Africa.</t>
+  </si>
+  <si>
+    <t>Prof. D.</t>
+  </si>
+  <si>
+    <t>Yogi Goswami</t>
+  </si>
+  <si>
+    <t>d.yogi@testmail.com</t>
+  </si>
+  <si>
+    <t>Clean Energy Research Center</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Prof. D. Yogi Goswami is a Distinguished Professor and Director of the Clean Energy Research Center at the University of South Florida. He is the Editor-in-Chief of Solar Compass, journal of the International Solar Alliance and Emeritus Editor-in-Chief of the Solar Energy journal. He is also the President-Elect of the Academy of Science, Engineering and Medicine of Florida.
+ Within the field of energy he has published 23 books, more than 400 papers, and holds 43 patents. He has made transformative contributions to the field of Solar Energy, including Thermodynamic Power Cycles, and Solar photocatalytic Detoxification and Disinfection of Air and Water. He developed a new combined Power and Cooling Cycle, now known as the Goswami Cycle, which has resulted in global research in a new class of Combined Cycles with multiple outputs.
+ He pioneered the development of photo-electrochemical oxidation (PECO) technology for disinfection of air, which is now available commercially. He has now developed the next generation Photonic technology to disinfect and detoxify the indoor air. Products based on this invention are helping allergy and asthma sufferers.
+ Prof. Goswami has served as the President of the International Solar Energy Society (ISES), and a Governor and Senior Vice President of ASME-International, among many professional leadership positions. As a leader in professional societies, he developed a number of energy policy options and impacted energy policies in many countries by direct interaction with their leaders.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="4">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin">
+        <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9A9A9A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9A9A9A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9A9A9A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9A9A9A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+  <cellXfs count="11">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -326,29 +669,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="3.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="4" max="4" width="26.44140625" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="8.21875" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10.25"/>
+    <col customWidth="1" min="2" max="2" width="11.88"/>
+    <col customWidth="1" min="3" max="3" width="27.5"/>
+    <col customWidth="1" min="4" max="4" width="50.13"/>
+    <col customWidth="1" min="5" max="5" width="23.63"/>
+    <col customWidth="1" min="6" max="6" width="8.25"/>
+    <col customWidth="1" min="7" max="7" width="51.38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -370,37 +710,405 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="G22" s="10"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="G23" s="10"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="G24" s="10"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="G26" s="10"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="G27" s="10"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="G28" s="10"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="G29" s="10"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="G31" s="10"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{05313194-77DD-4744-92B4-4592A4C79514}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>